--- a/basedatos_partidas/salida/descompuestos/CT-07-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-04-030.xlsx
@@ -591,10 +591,10 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="H12" t="n">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="13">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13.87</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>23.96</v>
+        <v>23.3</v>
       </c>
       <c r="H25" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>24.2</v>
+        <v>23.53</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-07-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-04-030.xlsx
@@ -565,10 +565,10 @@
         <v>0.22</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H11" t="n">
-        <v>4.84</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="12">
@@ -617,10 +617,10 @@
         <v>0.18</v>
       </c>
       <c r="G13" t="n">
-        <v>8.5</v>
+        <v>32</v>
       </c>
       <c r="H13" t="n">
-        <v>1.53</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13.21</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>23.3</v>
+        <v>43.59</v>
       </c>
       <c r="H25" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>23.53</v>
+        <v>44.03</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-07-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-04-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 07 Frisos y revestimientos de pared</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Enchapado de piedra natural</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
